--- a/Scripts_inesdattatreya/data_output/GS2_25-24_sessions/risk_ratio_satis_plot/Session_251007/NA_check_class_and_satisfaction_Session_251007.xlsx
+++ b/Scripts_inesdattatreya/data_output/GS2_25-24_sessions/risk_ratio_satis_plot/Session_251007/NA_check_class_and_satisfaction_Session_251007.xlsx
@@ -391,19 +391,19 @@
         <v>120</v>
       </c>
       <c r="B2">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
+        <v>60</v>
+      </c>
+      <c r="E2">
+        <v>25</v>
+      </c>
+      <c r="F2">
         <v>20</v>
-      </c>
-      <c r="E2">
-        <v>50</v>
-      </c>
-      <c r="F2">
-        <v>30</v>
       </c>
     </row>
   </sheetData>
